--- a/data/images.xlsx
+++ b/data/images.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Images" sheetId="1" r:id="rId1"/>
+    <sheet name="Categories" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,333 +398,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>label</v>
+        <v>name</v>
       </c>
       <c r="C1" t="str">
-        <v>url</v>
-      </c>
-      <c r="D1" t="str">
         <v>createdAt</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>img-001</v>
+        <v>cat-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Pexels Dog</v>
+        <v>عام</v>
       </c>
       <c r="C2" t="str">
-        <v>https://images.pexels.com/photos/802112/pexels-photo-802112.jpeg</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-02-21T00:04:56.454Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>img-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Pexels Cat</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://images.pexels.com/photos/572861/pexels-photo-572861.jpeg</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>img-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Pexels Bird</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://images.pexels.com/photos/2674052/pexels-photo-2674052.jpeg</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>img-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Pexels Deer</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://images.pexels.com/photos/247376/pexels-photo-247376.jpeg</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>img-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Pexels Antler</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://images.pexels.com/photos/34231/antler-antler-carrier-fallow-deer-hirsch.jpg</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>img-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Mountain Lake</v>
-      </c>
-      <c r="C7" t="str">
-        <v>https://images.pexels.com/photos/417173/pexels-photo-417173.jpeg</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>img-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>City Night</v>
-      </c>
-      <c r="C8" t="str">
-        <v>https://images.pexels.com/photos/338515/pexels-photo-338515.jpeg</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>img-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Forest Trail</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://images.pexels.com/photos/4827/nature-forest-trees-fog.jpeg</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>img-009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Coffee Cup</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://images.pexels.com/photos/302899/pexels-photo-302899.jpeg</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>img-010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Laptop Desk</v>
-      </c>
-      <c r="C11" t="str">
-        <v>https://images.pexels.com/photos/18105/pexels-photo.jpg</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>img-011</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Vintage Camera</v>
-      </c>
-      <c r="C12" t="str">
-        <v>https://images.pexels.com/photos/90946/pexels-photo-90946.jpeg</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>img-012</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Football</v>
-      </c>
-      <c r="C13" t="str">
-        <v>https://images.pexels.com/photos/47730/the-ball-stadion-football-the-pitch-47730.jpeg</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>img-013</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Pizza</v>
-      </c>
-      <c r="C14" t="str">
-        <v>https://images.pexels.com/photos/315755/pexels-photo-315755.jpeg</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>img-014</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Ice Cream</v>
-      </c>
-      <c r="C15" t="str">
-        <v>https://images.pexels.com/photos/1352278/pexels-photo-1352278.jpeg</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>img-015</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Rocket</v>
-      </c>
-      <c r="C16" t="str">
-        <v>https://images.pexels.com/photos/586063/pexels-photo-586063.jpeg</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>img-016</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Palm Tree</v>
-      </c>
-      <c r="C17" t="str">
-        <v>https://images.pexels.com/photos/457882/pexels-photo-457882.jpeg</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>img-017</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Castle</v>
-      </c>
-      <c r="C18" t="str">
-        <v>https://images.pexels.com/photos/161154/castle-hluboka-czech-republic-architecture-161154.jpeg</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>img-018</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Guitar</v>
-      </c>
-      <c r="C19" t="str">
-        <v>https://images.pexels.com/photos/164938/pexels-photo-164938.jpeg</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>img-019</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Robot</v>
-      </c>
-      <c r="C20" t="str">
-        <v>https://images.pexels.com/photos/2599244/pexels-photo-2599244.jpeg</v>
-      </c>
-      <c r="D20" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>img-020</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Space</v>
-      </c>
-      <c r="C21" t="str">
-        <v>https://images.pexels.com/photos/2159/flight-sky-earth-space.jpg</v>
-      </c>
-      <c r="D21" t="str">
-        <v>2026-02-21T00:04:56.455Z</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>img-1771632415619</v>
-      </c>
-      <c r="B22" t="str">
-        <v>omar</v>
-      </c>
-      <c r="C22" t="str">
-        <v>https://images.pexels.com/photos/667201/pexels-photo-667201.jpeg</v>
-      </c>
-      <c r="D22" t="str">
-        <v>2026-02-21T00:06:55.619Z</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>img-1771632451515</v>
-      </c>
-      <c r="B23" t="str">
-        <v>dd</v>
-      </c>
-      <c r="C23" t="str">
-        <v>https://images.pexels.com/photos/1059823/pexels-photo-1059823.jpeg</v>
-      </c>
-      <c r="D23" t="str">
-        <v>2026-02-21T00:07:31.515Z</v>
+        <v>2026-02-21T22:16:03.648Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/images.xlsx
+++ b/data/images.xlsx
@@ -398,17 +398,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>url</v>
+      </c>
+      <c r="E1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>img-1771714971103</v>
+      </c>
+      <c r="B2" t="str">
+        <v>سعاد</v>
+      </c>
+      <c r="C2" t="str">
+        <v>باب الحارة</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://i.ytimg.com/vi/sWaza53Cs90/maxresdefault.jpg?sqp=-oaymwEmCIAKENAF8quKqQMa8AEB-AH-CYAC0AWKAgwIABABGFsgTihlMA8=&amp;rs=AOn4CLD34TVEJa_5U4E5Vf3AZBI1Hig5ZQ</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-02-21T23:02:51.103Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>img-1771714991978</v>
+      </c>
+      <c r="B3" t="str">
+        <v>خيرية</v>
+      </c>
+      <c r="C3" t="str">
+        <v>باب الحارة</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://i1.wp.com/www.assawsana.com/portal/image/imgid399490.jpg?w=600&amp;ulb=true</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-02-21T23:03:11.978Z</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,12 +481,23 @@
         <v>عام</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-21T22:16:03.648Z</v>
+        <v>2026-02-21T23:03:31.523Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>cat-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>باب الحارة</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-21T23:03:31.523Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/images.xlsx
+++ b/data/images.xlsx
@@ -481,7 +481,7 @@
         <v>عام</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-21T23:03:31.523Z</v>
+        <v>2026-02-21T23:22:27.361Z</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
         <v>باب الحارة</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-21T23:03:31.523Z</v>
+        <v>2026-02-21T23:22:27.361Z</v>
       </c>
     </row>
   </sheetData>

--- a/data/images.xlsx
+++ b/data/images.xlsx
@@ -1,42 +1,162 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\who-i-am\who-i-am\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5157B4-84DE-4792-AAE6-C12C358A5376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Images" sheetId="1" r:id="rId1"/>
     <sheet name="Categories" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>img-1771714971103</t>
+  </si>
+  <si>
+    <t>سعاد</t>
+  </si>
+  <si>
+    <t>باب الحارة</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/sWaza53Cs90/maxresdefault.jpg?sqp=-oaymwEmCIAKENAF8quKqQMa8AEB-AH-CYAC0AWKAgwIABABGFsgTihlMA8=&amp;rs=AOn4CLD34TVEJa_5U4E5Vf3AZBI1Hig5ZQ</t>
+  </si>
+  <si>
+    <t>2026-02-21T23:02:51.103Z</t>
+  </si>
+  <si>
+    <t>img-1771714991978</t>
+  </si>
+  <si>
+    <t>خيرية</t>
+  </si>
+  <si>
+    <t>https://i1.wp.com/www.assawsana.com/portal/image/imgid399490.jpg?w=600&amp;ulb=true</t>
+  </si>
+  <si>
+    <t>2026-02-21T23:03:11.978Z</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>cat-001</t>
+  </si>
+  <si>
+    <t>عام</t>
+  </si>
+  <si>
+    <t>2026-02-21T23:22:27.361Z</t>
+  </si>
+  <si>
+    <t>cat-002</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR1hpZb9jxO3I_tbBAt5bd4PfxphaBgNR28fQ&amp;s</t>
+  </si>
+  <si>
+    <t>معتز</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRT9DizjqvFFW8pnPg3fL6DPhZAfI_fRCvNyA&amp;s</t>
+  </si>
+  <si>
+    <t>عصام</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSGrTNLOrIxypNxfeGrl3vF4kQNlY_cV1Ngmg&amp;s</t>
+  </si>
+  <si>
+    <t>ابو شهاب</t>
+  </si>
+  <si>
+    <t>https://cnn-arabic-images.cnn.io/cloudinary/image/upload/w_780,h_439,c_fill,q_auto/cnnarabic/2016/06/05/images/45041.jpg</t>
+  </si>
+  <si>
+    <t>جولي</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSll1olLhf884YfkKGmtXtTfBQmoRDA1h4mpQ&amp;s</t>
+  </si>
+  <si>
+    <t>لطفية</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTXVCTl7vXIEjf75aoXdZPfj6F3tufhrE06dQ&amp;s</t>
+  </si>
+  <si>
+    <t>دلال</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRim2Z_KIDhYQSyuaswDTlrW4SY05znlh9PbA&amp;s</t>
+  </si>
+  <si>
+    <t>جميلة</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQsPYpGMu0PzEgP8IZM02-AWXjuCcm--0HAYQ&amp;s</t>
+  </si>
+  <si>
+    <t>ابو ابراهيم</t>
+  </si>
+  <si>
+    <t>https://www.wattan.net/data/image/794x466/05104032551628300864670638308231.jpg</t>
+  </si>
+  <si>
+    <t>قطايف</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/3wQ-l8XMirE/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>ابو بدر</t>
+  </si>
+  <si>
+    <t>https://pbs.twimg.com/media/FQy4142XoAAdwZM.jpg</t>
+  </si>
+  <si>
+    <t>زهرة</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRQfhDoR0Iz7_YKcBY-AlkRAiR3R-SC1PrNEw&amp;s</t>
+  </si>
+  <si>
+    <t>النمس</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,13 +186,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,107 +525,279 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>label</v>
-      </c>
-      <c r="C1" t="str">
-        <v>category</v>
-      </c>
-      <c r="D1" t="str">
-        <v>url</v>
-      </c>
-      <c r="E1" t="str">
-        <v>createdAt</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>img-1771714971103</v>
-      </c>
-      <c r="B2" t="str">
-        <v>سعاد</v>
-      </c>
-      <c r="C2" t="str">
-        <v>باب الحارة</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://i.ytimg.com/vi/sWaza53Cs90/maxresdefault.jpg?sqp=-oaymwEmCIAKENAF8quKqQMa8AEB-AH-CYAC0AWKAgwIABABGFsgTihlMA8=&amp;rs=AOn4CLD34TVEJa_5U4E5Vf3AZBI1Hig5ZQ</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-02-21T23:02:51.103Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>img-1771714991978</v>
-      </c>
-      <c r="B3" t="str">
-        <v>خيرية</v>
-      </c>
-      <c r="C3" t="str">
-        <v>باب الحارة</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://i1.wp.com/www.assawsana.com/portal/image/imgid399490.jpg?w=600&amp;ulb=true</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-02-21T23:03:11.978Z</v>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError sqref="A1:E2 A3:B3 D3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>createdAt</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>cat-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>عام</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-02-21T23:22:27.361Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>cat-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>باب الحارة</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-02-21T23:22:27.361Z</v>
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError sqref="A1:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>